--- a/vrcc.xlsx
+++ b/vrcc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidackuaku/Desktop/Home Stuffs/M2/Apps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51135D5-DD70-F440-9443-EE01CA957989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08EFFD04-07D7-6A48-A0F6-CA81E089AAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{690D29BB-E107-B54C-8AFA-AAD6A1551766}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>District</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>24hr economy market</t>
+  </si>
+  <si>
+    <t>web_address</t>
   </si>
 </sst>
 </file>
@@ -528,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773B53BD-F917-6C4E-8253-31D0BBDF4EF2}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
@@ -540,7 +543,7 @@
     <col min="10" max="10" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -571,8 +574,11 @@
       <c r="J1" t="s">
         <v>18</v>
       </c>
+      <c r="K1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" ht="76">
+    <row r="2" spans="1:11" ht="76">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -604,7 +610,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="18">
+    <row r="3" spans="1:11" ht="18">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -630,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="95">
+    <row r="4" spans="1:11" ht="95">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -656,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>19</v>
       </c>
